--- a/tests/database/test_database_invalid_isotope_id.xlsx
+++ b/tests/database/test_database_invalid_isotope_id.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5942562C-00F8-BA43-8585-77F525C33F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C08DAB9-B675-0741-831F-77C29DD91636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="40">
   <si>
     <t>ID</t>
   </si>
@@ -150,6 +150,9 @@
   </si>
   <si>
     <t>undefined_species</t>
+  </si>
+  <si>
+    <t>M-4 Isotope</t>
   </si>
 </sst>
 </file>
@@ -516,19 +519,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="4" max="4" width="20.5" customWidth="1"/>
     <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -545,16 +549,19 @@
         <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -569,12 +576,13 @@
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="3">
+      <c r="G2" s="1"/>
+      <c r="H2" s="3">
         <v>1.5</v>
       </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -590,13 +598,16 @@
       <c r="E3" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="1"/>
-      <c r="G3" s="3"/>
-      <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1"/>
+      <c r="H3" s="3"/>
+      <c r="I3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -612,12 +623,12 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H4" s="3"/>
+      <c r="I4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -633,12 +644,12 @@
       <c r="E5" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="3"/>
+      <c r="I5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -654,12 +665,12 @@
       <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="3"/>
+      <c r="I6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -672,12 +683,12 @@
       <c r="D7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="3"/>
+      <c r="I7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -690,12 +701,12 @@
       <c r="D8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="3"/>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -708,12 +719,12 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="3"/>
+      <c r="I9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -726,12 +737,12 @@
       <c r="D10" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="3"/>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -744,15 +755,15 @@
       <c r="D11" t="s">
         <v>21</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>3</v>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H11" s="3"/>
+      <c r="I11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -765,15 +776,15 @@
       <c r="D12" t="s">
         <v>21</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>4</v>
       </c>
-      <c r="G12" s="3"/>
-      <c r="H12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H12" s="3"/>
+      <c r="I12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -786,15 +797,15 @@
       <c r="D13" t="s">
         <v>21</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>5</v>
       </c>
-      <c r="G13" s="3"/>
-      <c r="H13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H13" s="3"/>
+      <c r="I13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -807,11 +818,11 @@
       <c r="D14" t="s">
         <v>12</v>
       </c>
-      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J1:P13">
-    <sortCondition ref="L1:L13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="K1:Q13">
+    <sortCondition ref="M1:M13"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tests/database/test_database_invalid_isotope_id.xlsx
+++ b/tests/database/test_database_invalid_isotope_id.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/u0065634/Documents/Software_projects/LipidQMap/tests/database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C08DAB9-B675-0741-831F-77C29DD91636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E5D66A7-054A-8E43-8AAB-ECE129E129A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -89,9 +89,6 @@
     <t>IS</t>
   </si>
   <si>
-    <t>IS amount (pmol / mm2)</t>
-  </si>
-  <si>
     <t>M-2 Isotope</t>
   </si>
   <si>
@@ -153,6 +150,9 @@
   </si>
   <si>
     <t>M-4 Isotope</t>
+  </si>
+  <si>
+    <t>Standard amount (pmol / mm2)</t>
   </si>
 </sst>
 </file>
@@ -537,25 +537,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>17</v>
@@ -566,13 +566,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -584,19 +584,19 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
         <v>36</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
         <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>38</v>
       </c>
       <c r="F3" t="s">
         <v>6</v>
@@ -612,13 +612,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -633,13 +633,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -654,13 +654,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -675,13 +675,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" t="s">
@@ -693,13 +693,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" t="s">
@@ -711,13 +711,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" t="s">
@@ -729,13 +729,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
         <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" t="s">
@@ -747,13 +747,13 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
         <v>3</v>
@@ -768,13 +768,13 @@
         <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G12" t="s">
         <v>4</v>
@@ -789,13 +789,13 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
         <v>2</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
         <v>5</v>
@@ -810,7 +810,7 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
